--- a/Document/Note.xlsx
+++ b/Document/Note.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tantq\src\AppSuite\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tantq\src\AppSuite\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6671C67-8D68-4116-B147-260F225DD9ED}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF181585-0186-4997-B89E-C6980D67C42E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -285,10 +285,11 @@
     <t>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</t>
   </si>
   <si>
-    <t>client_secret_402369890551-q96ua475kbmsufigl2g5c86fiir6okp8.apps.googleusercontent.com.json</t>
-  </si>
-  <si>
     <t>{"installed":{"client_id":"402369890551-q96ua475kbmsufigl2g5c86fiir6okp8.apps.googleusercontent.com","project_id":"me-ron","auth_uri":"https://accounts.google.com/o/oauth2/auth","token_uri":"https://oauth2.googleapis.com/token","auth_provider_x509_cert_url":"https://www.googleapis.com/oauth2/v1/certs","client_secret":"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","redirect_uris":["http://localhost"]}}</t>
+  </si>
+  <si>
+    <t>AppSuite\Modules\MeRon\Assets\client_secret_402369890551-q96ua475kbmsufigl2g5c86fiir6okp8.apps.googleusercontent.com.json</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -773,12 +774,12 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
